--- a/tables/Table S11.xlsx
+++ b/tables/Table S11.xlsx
@@ -763,7 +763,11 @@
           <t>Ofaveolata016428</t>
         </is>
       </c>
-      <c r="D9" s="3" t="n"/>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>IPR001315</t>
+        </is>
+      </c>
       <c r="E9" s="4" t="n"/>
       <c r="F9" s="4" t="inlineStr">
         <is>
@@ -772,7 +776,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>NA [CARD domain]</t>
         </is>
       </c>
     </row>
@@ -936,7 +940,11 @@
           <t>Ssiderea022904</t>
         </is>
       </c>
-      <c r="D15" s="3" t="n"/>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
           <t>Fv/Fm</t>
@@ -949,7 +957,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>NA [no InterPro match]</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1060,11 @@
           <t>Ssiderea026926</t>
         </is>
       </c>
-      <c r="D19" s="3" t="n"/>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
       <c r="E19" s="4" t="n"/>
       <c r="F19" s="4" t="inlineStr">
         <is>
@@ -1061,7 +1073,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>NA [no InterPro match]</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1148,11 @@
           <t>Ssiderea004405</t>
         </is>
       </c>
-      <c r="D22" s="3" t="n"/>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
           <t>Acidified</t>
@@ -1149,7 +1165,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>NA [no InterPro match]</t>
         </is>
       </c>
     </row>
